--- a/Data/Terminator_Strength-250311.xlsx
+++ b/Data/Terminator_Strength-250311.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/zw24976_bristol_ac_uk/Documents/Documents/BCL/PhagePol_Terminators/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/zw24976_bristol_ac_uk/Documents/Documents/BCL/PhagePol_Terminators/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{71B608B9-0199-4337-A211-9633B1527558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D83CD22F-E425-4DCC-882E-5858F4446959}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{71B608B9-0199-4337-A211-9633B1527558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{108B5467-2435-4259-925E-03662C94AB62}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{AD5C4DDB-D741-4A9A-92C6-6FDEC50D1E81}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AD5C4DDB-D741-4A9A-92C6-6FDEC50D1E81}"/>
   </bookViews>
   <sheets>
-    <sheet name="RFP" sheetId="1" r:id="rId1"/>
-    <sheet name="GFP" sheetId="3" r:id="rId2"/>
-    <sheet name="OD600" sheetId="4" r:id="rId3"/>
+    <sheet name="PlateMap" sheetId="5" r:id="rId1"/>
+    <sheet name="RFP" sheetId="1" r:id="rId2"/>
+    <sheet name="GFP" sheetId="3" r:id="rId3"/>
+    <sheet name="OD600" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="38">
   <si>
     <t>G1</t>
   </si>
@@ -118,6 +119,48 @@
   </si>
   <si>
     <t>H12</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Blank</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>DH10B-TT7hyb1</t>
+  </si>
+  <si>
+    <t>MQ637-TT7hyb1</t>
+  </si>
+  <si>
+    <t>DH10B-noTer</t>
+  </si>
+  <si>
+    <t>pSHNJ200</t>
   </si>
 </sst>
 </file>
@@ -488,6 +531,160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF95C9B0-F14F-4B1D-8361-C898533A1F2F}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D45619D-B0F4-4AC8-A86A-B22DD48BF598}">
   <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -645,7 +842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACF42D9E-E19B-411F-9C3A-979D90E59BF9}">
   <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -803,7 +1000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29615F05-9A90-41E9-B5D9-D3CA3F0488A9}">
   <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
